--- a/artfynd/A 35848-2026 artfynd.xlsx
+++ b/artfynd/A 35848-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ31"/>
+  <dimension ref="A1:AZ35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1156,10 +1156,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>102237641</v>
+        <v>136361538</v>
       </c>
       <c r="B6" t="n">
-        <v>43251</v>
+        <v>45063</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1167,21 +1167,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102923</v>
+        <v>102021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettkantad guldvinge</t>
+          <t>Mindre bastardsvärmare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycaena hippothoe</t>
+          <t>Zygaena viciae</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1760)</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1198,7 +1198,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>friflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1238,12 +1238,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-07-13</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-07-13</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1270,45 +1270,57 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102237641</t>
+          <t>https://artportalen.se/Sighting/136361538</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125860250</v>
+        <v>102237641</v>
       </c>
       <c r="B7" t="n">
-        <v>61491</v>
+        <v>43251</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106670</v>
+        <v>102923</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart skogssnigel</t>
+          <t>Violettkantad guldvinge</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Arion ater ater</t>
+          <t>Lycaena hippothoe</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1760)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1346,12 +1358,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2022-07-13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2022-07-13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1378,16 +1390,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125860250</t>
+          <t>https://artportalen.se/Sighting/102237641</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>110021806</v>
+        <v>125860250</v>
       </c>
       <c r="B8" t="n">
-        <v>43219</v>
+        <v>61491</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1395,32 +1407,28 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>201028</v>
+        <v>106670</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre tåtelsmygare</t>
+          <t>Svart skogssnigel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Thymelicus lineola</t>
+          <t>Arion ater ater</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ochsenheimer, 1808)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1428,13 +1436,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>492342</v>
+        <v>492339</v>
       </c>
       <c r="R8" t="n">
         <v>6424648</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1458,12 +1466,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-06-11</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-06-11</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1490,38 +1498,38 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110021806</t>
+          <t>https://artportalen.se/Sighting/125860250</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113745780</v>
+        <v>110021806</v>
       </c>
       <c r="B9" t="n">
-        <v>43378</v>
+        <v>43219</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>201075</v>
+        <v>201028</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brunfläckig pärlemorfjäril</t>
+          <t>Mindre tåtelsmygare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Boloria selene</t>
+          <t>Thymelicus lineola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Ochsenheimer, 1808)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1602,55 +1610,47 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113745780</t>
+          <t>https://artportalen.se/Sighting/110021806</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>95105475</v>
+        <v>113745780</v>
       </c>
       <c r="B10" t="n">
-        <v>43328</v>
+        <v>43378</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>201122</v>
+        <v>201075</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Almsnabbvinge</t>
+          <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Satyrium w-album</t>
+          <t>Boloria selene</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Knoch, 1782)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1690,12 +1690,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-07-20</t>
+          <t>2023-06-11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-07-20</t>
+          <t>2023-06-11</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1722,16 +1722,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95105475</t>
+          <t>https://artportalen.se/Sighting/113745780</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>110783980</v>
+        <v>95105475</v>
       </c>
       <c r="B11" t="n">
-        <v>43258</v>
+        <v>43328</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1739,21 +1739,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>201129</v>
+        <v>201122</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitfläckig guldvinge</t>
+          <t>Almsnabbvinge</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycaena virgaureae</t>
+          <t>Satyrium w-album</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Knoch, 1782)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1770,7 +1770,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>friflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1810,12 +1810,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-06-08</t>
+          <t>2021-07-20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-06-08</t>
+          <t>2021-07-20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1842,38 +1842,38 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110783980</t>
+          <t>https://artportalen.se/Sighting/95105475</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>110021794</v>
+        <v>110783980</v>
       </c>
       <c r="B12" t="n">
-        <v>43285</v>
+        <v>43258</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>201143</v>
+        <v>201129</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ängsblåvinge</t>
+          <t>Vitfläckig guldvinge</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cyaniris semiargus</t>
+          <t>Lycaena virgaureae</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Rottemburg, 1775)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1882,7 +1882,11 @@
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
@@ -1926,12 +1930,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-06-11</t>
+          <t>2023-06-08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-06-11</t>
+          <t>2023-06-08</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1958,51 +1962,59 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110021794</t>
+          <t>https://artportalen.se/Sighting/110783980</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>110783931</v>
+        <v>136362614</v>
       </c>
       <c r="B13" t="n">
-        <v>43309</v>
+        <v>43271</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>201146</v>
+        <v>201129</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Silverblåvinge</t>
+          <t>Vitfläckig guldvinge</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Polyommatus amandus</t>
+          <t>Lycaena virgaureae</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schneider, 1792)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>imago/adult</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>friflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2012,13 +2024,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>492342</v>
+        <v>492339</v>
       </c>
       <c r="R13" t="n">
         <v>6424648</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2042,12 +2054,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-06-24</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-06-24</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2074,16 +2086,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110783931</t>
+          <t>https://artportalen.se/Sighting/136362614</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134838104</v>
+        <v>110021794</v>
       </c>
       <c r="B14" t="n">
-        <v>43314</v>
+        <v>43285</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2091,21 +2103,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>201146</v>
+        <v>201143</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Silverblåvinge</t>
+          <t>Ängsblåvinge</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Polyommatus amandus</t>
+          <t>Cyaniris semiargus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schneider, 1792)</t>
+          <t>(Rottemburg, 1775)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2114,16 +2126,8 @@
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>friflygande</t>
@@ -2136,13 +2140,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>492339</v>
+        <v>492342</v>
       </c>
       <c r="R14" t="n">
         <v>6424648</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2166,12 +2170,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2023-06-11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2023-06-11</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2198,51 +2202,51 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134838104</t>
+          <t>https://artportalen.se/Sighting/110021794</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>109102190</v>
+        <v>110783931</v>
       </c>
       <c r="B15" t="n">
-        <v>58826</v>
+        <v>43309</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>208242</v>
+        <v>201146</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Silverblåvinge</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Polyommatus amandus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schneider, 1792)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2282,12 +2286,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-05-14</t>
+          <t>2023-06-24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-05-14</t>
+          <t>2023-06-24</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2314,38 +2318,38 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109102190</t>
+          <t>https://artportalen.se/Sighting/110783931</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133529221</v>
+        <v>134838104</v>
       </c>
       <c r="B16" t="n">
-        <v>58848</v>
+        <v>43314</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>208242</v>
+        <v>201146</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Silverblåvinge</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Polyommatus amandus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schneider, 1792)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2356,7 +2360,7 @@
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2366,7 +2370,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>i vatten/simmande</t>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2406,12 +2410,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2438,33 +2442,33 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133529221</t>
+          <t>https://artportalen.se/Sighting/134838104</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117937189</v>
+        <v>136362295</v>
       </c>
       <c r="B17" t="n">
-        <v>58790</v>
+        <v>45056</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>208245</v>
+        <v>201164</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Sexfläckig bastardsvärmare</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Zygaena filipendulae</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2472,12 +2476,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>pheromone</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Taleryd  (trädgård), Sm</t>
@@ -2514,12 +2534,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2546,33 +2566,33 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117937189</t>
+          <t>https://artportalen.se/Sighting/136362295</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>86590519</v>
+        <v>109102190</v>
       </c>
       <c r="B18" t="n">
-        <v>41972</v>
+        <v>58826</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>213797</v>
+        <v>208242</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Humlerotfjäril</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepialus humuli</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2586,35 +2606,27 @@
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>vilande</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>ljusfälla</t>
-        </is>
-      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Taleryd  (trädgård), Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492339</v>
+        <v>492342</v>
       </c>
       <c r="R18" t="n">
         <v>6424648</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2638,12 +2650,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2020-06-28</t>
+          <t>2023-05-14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2020-06-28</t>
+          <t>2023-05-14</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2670,33 +2682,33 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86590519</t>
+          <t>https://artportalen.se/Sighting/109102190</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113741497</v>
+        <v>133529221</v>
       </c>
       <c r="B19" t="n">
-        <v>41972</v>
+        <v>58848</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>213797</v>
+        <v>208242</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Humlerotfjäril</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepialus humuli</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2710,31 +2722,35 @@
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>ljusfälla</t>
-        </is>
-      </c>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Taleryd  (trädgård), Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>492342</v>
+        <v>492339</v>
       </c>
       <c r="R19" t="n">
         <v>6424648</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2758,12 +2774,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-06-09</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-06-09</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2790,16 +2806,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113741497</t>
+          <t>https://artportalen.se/Sighting/133529221</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117494358</v>
+        <v>117937189</v>
       </c>
       <c r="B20" t="n">
-        <v>40300</v>
+        <v>58790</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2807,50 +2823,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>214803</v>
+        <v>208245</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>pheromone</t>
-        </is>
-      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Taleryd  (trädgård), Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>492342</v>
+        <v>492339</v>
       </c>
       <c r="R20" t="n">
         <v>6424648</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2874,12 +2882,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-06-02</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-06-02</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2906,16 +2914,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117494358</t>
+          <t>https://artportalen.se/Sighting/117937189</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117935757</v>
+        <v>136363168</v>
       </c>
       <c r="B21" t="n">
-        <v>40300</v>
+        <v>56909</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,41 +2931,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>214803</v>
+        <v>208257</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>imago/adult</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>pheromone</t>
-        </is>
-      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Taleryd  (trädgård), Sm</t>
@@ -2994,12 +2998,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-06-21</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-06-21</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3026,33 +3030,33 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117935757</t>
+          <t>https://artportalen.se/Sighting/136363168</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>101720738</v>
+        <v>86590519</v>
       </c>
       <c r="B22" t="n">
-        <v>40269</v>
+        <v>41972</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>214815</v>
+        <v>213797</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Större träfjäril</t>
+          <t>Humlerotfjäril</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cossus cossus</t>
+          <t>Hepialus humuli</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3072,7 +3076,11 @@
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr">
         <is>
           <t>ljusfälla</t>
@@ -3114,12 +3122,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2022-06-16</t>
+          <t>2020-06-28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2022-06-16</t>
+          <t>2020-06-28</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3146,33 +3154,33 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101720738</t>
+          <t>https://artportalen.se/Sighting/86590519</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>115237082</v>
+        <v>113741497</v>
       </c>
       <c r="B23" t="n">
-        <v>40269</v>
+        <v>41972</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>214815</v>
+        <v>213797</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Större träfjäril</t>
+          <t>Humlerotfjäril</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cossus cossus</t>
+          <t>Hepialus humuli</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3187,7 +3195,11 @@
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
@@ -3230,12 +3242,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2022-06-16</t>
+          <t>2023-06-09</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2022-06-16</t>
+          <t>2023-06-09</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3262,56 +3274,52 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115237082</t>
+          <t>https://artportalen.se/Sighting/113741497</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>101720697</v>
+        <v>117494358</v>
       </c>
       <c r="B24" t="n">
-        <v>43875</v>
+        <v>40300</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>215467</v>
+        <v>214803</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kvadratmott</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Udea olivalis</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>ljusfälla</t>
+          <t>pheromone</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3320,13 +3328,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492339</v>
+        <v>492342</v>
       </c>
       <c r="R24" t="n">
         <v>6424648</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3350,12 +3358,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2022-06-16</t>
+          <t>2024-06-02</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2022-06-16</t>
+          <t>2024-06-02</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3382,48 +3390,56 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101720697</t>
+          <t>https://artportalen.se/Sighting/117494358</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113595554</v>
+        <v>117935757</v>
       </c>
       <c r="B25" t="n">
-        <v>43875</v>
+        <v>40300</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>215467</v>
+        <v>214803</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kvadratmott</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Udea olivalis</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Borkhausen, 1789)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>ljusfälla</t>
+          <t>pheromone</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3432,13 +3448,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>492342</v>
+        <v>492339</v>
       </c>
       <c r="R25" t="n">
         <v>6424648</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3462,12 +3478,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
+          <t>2024-06-21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
+          <t>2024-06-21</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3494,43 +3510,51 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113595554</t>
+          <t>https://artportalen.se/Sighting/117935757</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>115196117</v>
+        <v>101720738</v>
       </c>
       <c r="B26" t="n">
-        <v>41650</v>
+        <v>40269</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>215785</v>
+        <v>214815</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Brunflammig fältmätare</t>
+          <t>Större träfjäril</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Perizoma flavofasciata</t>
+          <t>Cossus cossus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Thunberg, 1792)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
@@ -3544,13 +3568,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>492342</v>
+        <v>492339</v>
       </c>
       <c r="R26" t="n">
         <v>6424648</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3574,12 +3598,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2022-08-11</t>
+          <t>2022-06-16</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2022-08-11</t>
+          <t>2022-06-16</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3606,59 +3630,67 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115196117</t>
+          <t>https://artportalen.se/Sighting/101720738</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>114585493</v>
+        <v>115237082</v>
       </c>
       <c r="B27" t="n">
-        <v>42516</v>
+        <v>40269</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>216123</v>
+        <v>214815</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre stamfly</t>
+          <t>Större träfjäril</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Amphipoea crinanensis</t>
+          <t>Cossus cossus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Burrows, 1908)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>ljusfälla</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Taleryd  (trädgård), Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>492339</v>
+        <v>492342</v>
       </c>
       <c r="R27" t="n">
         <v>6424648</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3682,12 +3714,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2021-08-02</t>
+          <t>2022-06-16</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2021-08-02</t>
+          <t>2022-06-16</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3714,16 +3746,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114585493</t>
+          <t>https://artportalen.se/Sighting/115237082</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>115196067</v>
+        <v>101720697</v>
       </c>
       <c r="B28" t="n">
-        <v>42516</v>
+        <v>43875</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3731,26 +3763,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>216123</v>
+        <v>215467</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre stamfly</t>
+          <t>Kvadratmott</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Amphipoea crinanensis</t>
+          <t>Udea olivalis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Burrows, 1908)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
@@ -3764,13 +3804,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>492342</v>
+        <v>492339</v>
       </c>
       <c r="R28" t="n">
         <v>6424648</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3794,12 +3834,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2022-08-07</t>
+          <t>2022-06-16</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2022-08-07</t>
+          <t>2022-06-16</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3826,16 +3866,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115196067</t>
+          <t>https://artportalen.se/Sighting/101720697</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126438005</v>
+        <v>113595554</v>
       </c>
       <c r="B29" t="n">
-        <v>42691</v>
+        <v>43875</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3843,30 +3883,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>216164</v>
+        <v>215467</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Praktnejlikfly</t>
+          <t>Kvadratmott</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hadena confusa</t>
+          <t>Udea olivalis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hufnagel, 1766)</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
@@ -3880,13 +3916,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>492339</v>
+        <v>492342</v>
       </c>
       <c r="R29" t="n">
         <v>6424648</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3910,12 +3946,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3942,38 +3978,38 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126438005</t>
+          <t>https://artportalen.se/Sighting/113595554</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>115127604</v>
+        <v>115196117</v>
       </c>
       <c r="B30" t="n">
-        <v>42696</v>
+        <v>41650</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>216169</v>
+        <v>215785</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gulbrunt nejlikfly</t>
+          <t>Brunflammig fältmätare</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hadena perplexa</t>
+          <t>Perizoma flavofasciata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Thunberg, 1792)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4022,12 +4058,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2022-05-08</t>
+          <t>2022-08-11</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2022-05-08</t>
+          <t>2022-08-11</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4054,48 +4090,45 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115127604</t>
+          <t>https://artportalen.se/Sighting/115196117</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132204344</v>
+        <v>114585493</v>
       </c>
       <c r="B31" t="n">
-        <v>101324</v>
+        <v>42516</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222782</v>
+        <v>216123</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitsippa</t>
+          <t>Mindre stamfly</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Anemone nemorosa</t>
+          <t>Amphipoea crinanensis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Burrows, 1908)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4133,12 +4166,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2021-08-02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2021-08-02</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4164,6 +4197,457 @@
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114585493</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>115196067</v>
+      </c>
+      <c r="B32" t="n">
+        <v>42516</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>216123</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Mindre stamfly</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Amphipoea crinanensis</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Burrows, 1908)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>ljusfälla</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Taleryd  (trädgård), Sm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>492342</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6424648</v>
+      </c>
+      <c r="S32" t="n">
+        <v>25</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Tranås</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Linderås</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2022-08-07</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2022-08-07</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Magnus Johansson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Magnus Johansson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115196067</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>126438005</v>
+      </c>
+      <c r="B33" t="n">
+        <v>42691</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>216164</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Praktnejlikfly</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Hadena confusa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Hufnagel, 1766)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>ljusfälla</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Taleryd  (trädgård), Sm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>492339</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6424648</v>
+      </c>
+      <c r="S33" t="n">
+        <v>4</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Tranås</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Linderås</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Magnus Johansson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Magnus Johansson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126438005</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>115127604</v>
+      </c>
+      <c r="B34" t="n">
+        <v>42696</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>216169</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Gulbrunt nejlikfly</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hadena perplexa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>ljusfälla</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Taleryd  (trädgård), Sm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>492342</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6424648</v>
+      </c>
+      <c r="S34" t="n">
+        <v>25</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Tranås</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Linderås</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2022-05-08</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2022-05-08</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Magnus Johansson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Magnus Johansson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115127604</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>132204344</v>
+      </c>
+      <c r="B35" t="n">
+        <v>101324</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>222782</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Vitsippa</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Anemone nemorosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Taleryd  (trädgård), Sm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>492339</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6424648</v>
+      </c>
+      <c r="S35" t="n">
+        <v>4</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Tranås</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Linderås</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Magnus Johansson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Magnus Johansson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/132204344</t>
         </is>
@@ -4201,6 +4685,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35848-2026 artfynd.xlsx
+++ b/artfynd/A 35848-2026 artfynd.xlsx
@@ -1159,7 +1159,7 @@
         <v>136361538</v>
       </c>
       <c r="B6" t="n">
-        <v>45063</v>
+        <v>45068</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>136362614</v>
       </c>
       <c r="B13" t="n">
-        <v>43271</v>
+        <v>43276</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>136362295</v>
       </c>
       <c r="B17" t="n">
-        <v>45056</v>
+        <v>45061</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>136363168</v>
       </c>
       <c r="B21" t="n">
-        <v>56909</v>
+        <v>56914</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 35848-2026 artfynd.xlsx
+++ b/artfynd/A 35848-2026 artfynd.xlsx
@@ -1159,7 +1159,7 @@
         <v>136361538</v>
       </c>
       <c r="B6" t="n">
-        <v>45068</v>
+        <v>45081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>136362614</v>
       </c>
       <c r="B13" t="n">
-        <v>43276</v>
+        <v>43289</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>136362295</v>
       </c>
       <c r="B17" t="n">
-        <v>45061</v>
+        <v>45074</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>136363168</v>
       </c>
       <c r="B21" t="n">
-        <v>56914</v>
+        <v>56927</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
